--- a/meridian-data-v2/Corvina_Quarter_BPO-0441_Order_Schedule.xlsx
+++ b/meridian-data-v2/Corvina_Quarter_BPO-0441_Order_Schedule.xlsx
@@ -649,7 +649,7 @@
     <row r="13">
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>APPLIANCES - delivery schedule SCH-0441-01</t>
+          <t>APPLIANCES - delivery schedule SCH-0141-01</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
     <row r="44">
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>TAPWARE &amp; SANITARYWARE - delivery schedule SCH-0441-02</t>
+          <t>TAPWARE &amp; SANITARYWARE - delivery schedule SCH-0141-02</t>
         </is>
       </c>
     </row>
